--- a/output/2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sede legale a Samobor (Zagrebačka županija; produttore leader croato di impianti clima/ventilazione/clean room, incl. camere di filtrazione); filiale commerciale fisica confermata a Varaždin (Jalkovec) che serve le contee Varaždinska/Međimurska/parte Koprivničko-križevačka. Esistenza verificata via WebSearch (klimatizacija.hr/poslovnice/varazdin, companywall.hr).</t>
+          <t>Sede legale a Samobor (Zagrebačka županija; produttore leader croato di impianti clima/ventilazione/clean room, incl. camere di filtrazione); filiale commerciale fisica confermata a Varaždin (Jalkovec) che serve le contee Varaždinska/Međimurska/parte Koprivničko-križevačka. Esistenza verificata via WebSearch (klimatizacija.hr/poslovnice/varazdin, companywall.hr). [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -526,7 +526,6 @@
           <t>+385 51 818 626</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Fornitore extra-provinciale (sede reale in Primorsko-goranska, non Varaždinska) ma rilevante a livello nazionale per il settore depolverazione industriale. Esistenza e attività verificate via WebSearch (rgv.hr, tvrtke.hr, hrvatsko-trziste-rada.com.hr). Email non reperita: campo lasciato vuoto.</t>
@@ -564,10 +563,9 @@
           <t>+385 1 2910 110</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore extra-provinciale (sede reale a Zagabria, non Varaždinska) rilevante per il settore depolverazione. Azienda dal 1992, ISO 9001/14001. Esistenza verificata via WebSearch (filtan.hr, companywall.hr, fininfo.hr). Email non reperita: campo lasciato vuoto.</t>
+          <t>Fornitore extra-provinciale (sede reale a Zagabria, non Varaždinska) rilevante per il settore depolverazione. Azienda dal 1992, ISO 9001/14001. Esistenza verificata via WebSearch (filtan.hr, companywall.hr, fininfo.hr). Email non reperita: campo lasciato vuoto. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
